--- a/4P_Index_NS_05-062_Pollution_Atmosphérique.xlsx
+++ b/4P_Index_NS_05-062_Pollution_Atmosphérique.xlsx
@@ -635,11 +635,7 @@
       <c r="M2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>No explicit budget, fee or economic instrument in the standard. Monitoring and measurement costs are borne by the operator (Ch. V, §5).</t>
-        </is>
-      </c>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="3">
         <f>AVERAGE(G2,I2,K2,M2,P2)</f>
         <v/>
@@ -649,7 +645,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Disposal</t>
+          <t>End of life</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -732,11 +728,7 @@
       <c r="M3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>No explicit budget, fee or economic instrument in the standard. Monitoring and measurement costs are borne by the operator (Ch. V, §5).</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="3">
         <f>AVERAGE(G3,I3,K3,M3,P3)</f>
         <v/>
@@ -829,11 +821,7 @@
       <c r="M4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>No explicit budget, fee or economic instrument in the standard. Monitoring and measurement costs are borne by the operator (Ch. V, §5).</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="3">
         <f>AVERAGE(G4,I4,K4,M4,P4)</f>
         <v/>
@@ -843,7 +831,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Disposal</t>
+          <t>End of life</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
